--- a/demo_output/figure_02_Danmark vs. Sverige — Inflation, CPI (%).xlsx
+++ b/demo_output/figure_02_Danmark vs. Sverige — Inflation, CPI (%).xlsx
@@ -8,8 +8,8 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Grafik" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danmark — Inflation, CPI (%)" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sverige — Inflation, CPI (%)" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sverige — Inflation, CPI" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Danmark — Inflation, CPI" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,7 +483,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Danmark — Inflation, CPI (%)</t>
+          <t>Sverige — Inflation, CPI</t>
         </is>
       </c>
     </row>
@@ -494,7 +494,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1.81781458291254</v>
+        <v>0.453170852576138</v>
       </c>
     </row>
     <row r="3">
@@ -504,7 +504,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1.92422138464584</v>
+        <v>1.36021468627693</v>
       </c>
     </row>
     <row r="4">
@@ -514,7 +514,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.69326586220324</v>
+        <v>2.21216883436733</v>
       </c>
     </row>
     <row r="5">
@@ -524,7 +524,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3.41626794258374</v>
+        <v>3.43704910602875</v>
       </c>
     </row>
     <row r="6">
@@ -534,7 +534,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1.30470991024335</v>
+        <v>-0.494460544378051</v>
       </c>
     </row>
     <row r="7">
@@ -544,7 +544,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>2.31092436974786</v>
+        <v>1.15798802715626</v>
       </c>
     </row>
     <row r="8">
@@ -554,7 +554,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2.7586822605125</v>
+        <v>2.9611507382214</v>
       </c>
     </row>
     <row r="9">
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>2.3979148566464</v>
+        <v>0.888377506923735</v>
       </c>
     </row>
     <row r="10">
@@ -574,7 +574,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>0.789071780078062</v>
+        <v>-0.044292970148682</v>
       </c>
     </row>
     <row r="11">
@@ -584,7 +584,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.56402054044954</v>
+        <v>-0.179638494114635</v>
       </c>
     </row>
     <row r="12">
@@ -594,7 +594,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>0.452034153691574</v>
+        <v>-0.0467847449832812</v>
       </c>
     </row>
     <row r="13">
@@ -604,7 +604,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0.250000000000031</v>
+        <v>0.984269244577992</v>
       </c>
     </row>
     <row r="14">
@@ -614,7 +614,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>1.14713216957601</v>
+        <v>1.79449904665599</v>
       </c>
     </row>
     <row r="15">
@@ -624,7 +624,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>0.813609467455631</v>
+        <v>1.95353530127028</v>
       </c>
     </row>
     <row r="16">
@@ -634,7 +634,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>0.75813157251162</v>
+        <v>1.78415097403835</v>
       </c>
     </row>
     <row r="17">
@@ -644,7 +644,7 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>0.420711974110024</v>
+        <v>0.497367318853572</v>
       </c>
     </row>
     <row r="18">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>1.85304543989689</v>
+        <v>2.16319736447143</v>
       </c>
     </row>
     <row r="19">
@@ -664,7 +664,7 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>7.69656699889259</v>
+        <v>8.36929098869189</v>
       </c>
     </row>
     <row r="20">
@@ -674,7 +674,7 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>3.30517811237605</v>
+        <v>8.5486248974891</v>
       </c>
     </row>
     <row r="21">
@@ -684,7 +684,7 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>1.37220049768925</v>
+        <v>2.83581658224034</v>
       </c>
     </row>
   </sheetData>
@@ -709,7 +709,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Sverige — Inflation, CPI (%)</t>
+          <t>Danmark — Inflation, CPI</t>
         </is>
       </c>
     </row>
@@ -720,7 +720,7 @@
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.453170852576138</v>
+        <v>1.81781458291254</v>
       </c>
     </row>
     <row r="3">
@@ -730,7 +730,7 @@
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1.36021468627693</v>
+        <v>1.92422138464584</v>
       </c>
     </row>
     <row r="4">
@@ -740,7 +740,7 @@
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2.21216883436733</v>
+        <v>1.69326586220324</v>
       </c>
     </row>
     <row r="5">
@@ -750,7 +750,7 @@
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3.43704910602875</v>
+        <v>3.41626794258374</v>
       </c>
     </row>
     <row r="6">
@@ -760,7 +760,7 @@
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>-0.494460544378051</v>
+        <v>1.30470991024335</v>
       </c>
     </row>
     <row r="7">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="B7" s="2" t="n">
-        <v>1.15798802715626</v>
+        <v>2.31092436974786</v>
       </c>
     </row>
     <row r="8">
@@ -780,7 +780,7 @@
         </is>
       </c>
       <c r="B8" s="2" t="n">
-        <v>2.9611507382214</v>
+        <v>2.7586822605125</v>
       </c>
     </row>
     <row r="9">
@@ -790,7 +790,7 @@
         </is>
       </c>
       <c r="B9" s="2" t="n">
-        <v>0.888377506923735</v>
+        <v>2.3979148566464</v>
       </c>
     </row>
     <row r="10">
@@ -800,7 +800,7 @@
         </is>
       </c>
       <c r="B10" s="2" t="n">
-        <v>-0.044292970148682</v>
+        <v>0.789071780078062</v>
       </c>
     </row>
     <row r="11">
@@ -810,7 +810,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>-0.179638494114635</v>
+        <v>0.56402054044954</v>
       </c>
     </row>
     <row r="12">
@@ -820,7 +820,7 @@
         </is>
       </c>
       <c r="B12" s="2" t="n">
-        <v>-0.0467847449832812</v>
+        <v>0.452034153691574</v>
       </c>
     </row>
     <row r="13">
@@ -830,7 +830,7 @@
         </is>
       </c>
       <c r="B13" s="2" t="n">
-        <v>0.984269244577992</v>
+        <v>0.250000000000031</v>
       </c>
     </row>
     <row r="14">
@@ -840,7 +840,7 @@
         </is>
       </c>
       <c r="B14" s="2" t="n">
-        <v>1.79449904665599</v>
+        <v>1.14713216957601</v>
       </c>
     </row>
     <row r="15">
@@ -850,7 +850,7 @@
         </is>
       </c>
       <c r="B15" s="2" t="n">
-        <v>1.95353530127028</v>
+        <v>0.813609467455631</v>
       </c>
     </row>
     <row r="16">
@@ -860,7 +860,7 @@
         </is>
       </c>
       <c r="B16" s="2" t="n">
-        <v>1.78415097403835</v>
+        <v>0.75813157251162</v>
       </c>
     </row>
     <row r="17">
@@ -870,7 +870,7 @@
         </is>
       </c>
       <c r="B17" s="2" t="n">
-        <v>0.497367318853572</v>
+        <v>0.420711974110024</v>
       </c>
     </row>
     <row r="18">
@@ -880,7 +880,7 @@
         </is>
       </c>
       <c r="B18" s="2" t="n">
-        <v>2.16319736447143</v>
+        <v>1.85304543989689</v>
       </c>
     </row>
     <row r="19">
@@ -890,7 +890,7 @@
         </is>
       </c>
       <c r="B19" s="2" t="n">
-        <v>8.36929098869189</v>
+        <v>7.69656699889259</v>
       </c>
     </row>
     <row r="20">
@@ -900,7 +900,7 @@
         </is>
       </c>
       <c r="B20" s="2" t="n">
-        <v>8.5486248974891</v>
+        <v>3.30517811237605</v>
       </c>
     </row>
     <row r="21">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="B21" s="2" t="n">
-        <v>2.83581658224034</v>
+        <v>1.37220049768925</v>
       </c>
     </row>
   </sheetData>

--- a/demo_output/figure_02_Danmark vs. Sverige — Inflation, CPI (%).xlsx
+++ b/demo_output/figure_02_Danmark vs. Sverige — Inflation, CPI (%).xlsx
@@ -472,7 +472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -490,200 +490,50 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2005-01-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>0.453170852576138</v>
+        <v>0.497367318853572</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1.36021468627693</v>
+        <v>2.16319736447143</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>2.21216883436733</v>
+        <v>8.36929098869189</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3.43704910602875</v>
+        <v>8.5486248974891</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>-0.494460544378051</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>1.15798802715626</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>2011-01-01</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>2.9611507382214</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>2012-01-01</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>0.888377506923735</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>2013-01-01</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>-0.044292970148682</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>-0.179638494114635</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>-0.0467847449832812</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>2016-01-01</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>0.984269244577992</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>2017-01-01</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>1.79449904665599</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>2018-01-01</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>1.95353530127028</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>2019-01-01</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>1.78415097403835</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>2020-01-01</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>0.497367318853572</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>2021-01-01</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>2.16319736447143</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>8.36929098869189</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>2023-01-01</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>8.5486248974891</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>2024-01-01</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
         <v>2.83581658224034</v>
       </c>
     </row>
@@ -698,7 +548,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B21"/>
+  <dimension ref="A1:B6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -716,200 +566,50 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>2005-01-01</t>
+          <t>2020-01-01</t>
         </is>
       </c>
       <c r="B2" s="2" t="n">
-        <v>1.81781458291254</v>
+        <v>0.420711974110024</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2006-01-01</t>
+          <t>2021-01-01</t>
         </is>
       </c>
       <c r="B3" s="2" t="n">
-        <v>1.92422138464584</v>
+        <v>1.85304543989689</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>2007-01-01</t>
+          <t>2022-01-01</t>
         </is>
       </c>
       <c r="B4" s="2" t="n">
-        <v>1.69326586220324</v>
+        <v>7.69656699889259</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2008-01-01</t>
+          <t>2023-01-01</t>
         </is>
       </c>
       <c r="B5" s="2" t="n">
-        <v>3.41626794258374</v>
+        <v>3.30517811237605</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2009-01-01</t>
+          <t>2024-01-01</t>
         </is>
       </c>
       <c r="B6" s="2" t="n">
-        <v>1.30470991024335</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>2010-01-01</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="n">
-        <v>2.31092436974786</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>2011-01-01</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="n">
-        <v>2.7586822605125</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>2012-01-01</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="n">
-        <v>2.3979148566464</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>2013-01-01</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n">
-        <v>0.789071780078062</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>2014-01-01</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="n">
-        <v>0.56402054044954</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>2015-01-01</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>0.452034153691574</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>2016-01-01</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>0.250000000000031</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>2017-01-01</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>1.14713216957601</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>2018-01-01</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="n">
-        <v>0.813609467455631</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>2019-01-01</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="n">
-        <v>0.75813157251162</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>2020-01-01</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>0.420711974110024</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>2021-01-01</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>1.85304543989689</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>2022-01-01</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>7.69656699889259</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>2023-01-01</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="n">
-        <v>3.30517811237605</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>2024-01-01</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="n">
         <v>1.37220049768925</v>
       </c>
     </row>
